--- a/artfynd/A 16101-2020 artfynd.xlsx
+++ b/artfynd/A 16101-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,6 +795,139 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122845695</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Olastorp 5, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>383904</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6685555</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Vi hör den nästan väjre gång vi är der</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Vivian Nielsen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Vivian Nielsen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16101-2020 artfynd.xlsx
+++ b/artfynd/A 16101-2020 artfynd.xlsx
@@ -798,7 +798,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122845695</v>
+        <v>122846231</v>
       </c>
       <c r="B3" t="n">
         <v>57494</v>
@@ -831,16 +831,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -884,27 +880,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Vi hör den nästan väjre gång vi är der</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 16101-2020 artfynd.xlsx
+++ b/artfynd/A 16101-2020 artfynd.xlsx
@@ -798,7 +798,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122846231</v>
+        <v>122845695</v>
       </c>
       <c r="B3" t="n">
         <v>57494</v>
@@ -831,12 +831,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -880,22 +884,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Vi hör den nästan väjre gång vi är der</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 16101-2020 artfynd.xlsx
+++ b/artfynd/A 16101-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122798865</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>122846231</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
